--- a/resources/qa_test/formula_samples/_test_formula_lookup.xlsx
+++ b/resources/qa_test/formula_samples/_test_formula_lookup.xlsx
@@ -105,22 +105,25 @@
       <color theme="1"/>
       <name val="Noto Sans SC"/>
       <family val="2"/>
-      <charset val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -243,69 +246,11 @@
         <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
